--- a/backend/Importacao_Auvo.xlsx
+++ b/backend/Importacao_Auvo.xlsx
@@ -832,7 +832,11 @@
           <t>Colaborador</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wilson - auxiliar</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
@@ -892,7 +896,11 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>08:00</t>
